--- a/textbook_examples/mod03_q04_power_query_answer.xlsx
+++ b/textbook_examples/mod03_q04_power_query_answer.xlsx
@@ -1580,18 +1580,18 @@
       <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="e">
-        <f>ROWS(#REF!)</f>
-        <v>#REF!</v>
+      <c r="B6" s="8">
+        <f>ROWS(q04_tickets)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="e">
-        <f>AVERAGE(#REF!)</f>
-        <v>#REF!</v>
+      <c r="B7" s="10">
+        <f>AVERAGE(q04_tickets[weight_tonnes])</f>
+        <v>30.165</v>
       </c>
     </row>
     <row r="8" spans="1:2">
